--- a/data/raw/inventory/Week 26/Nexlev/Inventory Snapshot.xlsx
+++ b/data/raw/inventory/Week 26/Nexlev/Inventory Snapshot.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="G:\Other computers\My Laptop\D\Nitesh\Weekly Report - B2B + B2C\FastAPI\data\raw\inventory\Week 26\Nexlev\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0A857C72-E5BD-48AC-958A-07CEB7444196}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C62160F4-12F9-4026-9C48-BD6A72F6CD4F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{D49B0F4C-5F9E-467E-8AD9-9E638F42404F}"/>
   </bookViews>
@@ -5660,10 +5660,13 @@
       <c r="I242" s="9">
         <v>2000</v>
       </c>
-      <c r="J242" s="7" t="s">
-        <v>204</v>
-      </c>
-      <c r="K242" s="8"/>
+      <c r="J242" s="7" t="str">
+        <f>K242</f>
+        <v>Pipeline</v>
+      </c>
+      <c r="K242" s="8" t="s">
+        <v>203</v>
+      </c>
     </row>
     <row r="243" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A243" s="4" t="s">
@@ -5678,10 +5681,13 @@
       <c r="I243" s="9">
         <v>2000</v>
       </c>
-      <c r="J243" s="7" t="s">
-        <v>204</v>
-      </c>
-      <c r="K243" s="8"/>
+      <c r="J243" s="7" t="str">
+        <f t="shared" ref="J243:J246" si="0">K243</f>
+        <v>Pipeline</v>
+      </c>
+      <c r="K243" s="8" t="s">
+        <v>203</v>
+      </c>
     </row>
     <row r="244" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A244" s="4" t="s">
@@ -5696,10 +5702,13 @@
       <c r="I244" s="9">
         <v>2000</v>
       </c>
-      <c r="J244" s="7" t="s">
-        <v>204</v>
-      </c>
-      <c r="K244" s="8"/>
+      <c r="J244" s="7" t="str">
+        <f t="shared" si="0"/>
+        <v>Pipeline</v>
+      </c>
+      <c r="K244" s="8" t="s">
+        <v>203</v>
+      </c>
     </row>
     <row r="245" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A245" s="4" t="s">
@@ -5714,10 +5723,13 @@
       <c r="I245" s="9">
         <v>996</v>
       </c>
-      <c r="J245" s="7" t="s">
-        <v>204</v>
-      </c>
-      <c r="K245" s="8"/>
+      <c r="J245" s="7" t="str">
+        <f t="shared" si="0"/>
+        <v>Pipeline</v>
+      </c>
+      <c r="K245" s="8" t="s">
+        <v>203</v>
+      </c>
     </row>
     <row r="246" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A246" s="6" t="s">
@@ -5732,10 +5744,13 @@
       <c r="I246" s="9">
         <v>405</v>
       </c>
-      <c r="J246" s="7" t="s">
-        <v>204</v>
-      </c>
-      <c r="K246" s="8"/>
+      <c r="J246" s="7" t="str">
+        <f t="shared" si="0"/>
+        <v>Pipeline</v>
+      </c>
+      <c r="K246" s="8" t="s">
+        <v>203</v>
+      </c>
     </row>
     <row r="247" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A247" s="4" t="s">
@@ -5750,10 +5765,13 @@
       <c r="I247" s="9">
         <v>2000</v>
       </c>
-      <c r="J247" s="7" t="s">
-        <v>203</v>
-      </c>
-      <c r="K247" s="8"/>
+      <c r="J247" s="7" t="str">
+        <f>K247</f>
+        <v>Open Order</v>
+      </c>
+      <c r="K247" s="8" t="s">
+        <v>204</v>
+      </c>
     </row>
     <row r="248" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A248" s="4" t="s">
@@ -5768,10 +5786,13 @@
       <c r="I248" s="9">
         <v>2000</v>
       </c>
-      <c r="J248" s="7" t="s">
-        <v>203</v>
-      </c>
-      <c r="K248" s="8"/>
+      <c r="J248" s="7" t="str">
+        <f t="shared" ref="J248:J255" si="1">K248</f>
+        <v>Open Order</v>
+      </c>
+      <c r="K248" s="8" t="s">
+        <v>204</v>
+      </c>
     </row>
     <row r="249" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A249" s="4" t="s">
@@ -5786,10 +5807,13 @@
       <c r="I249" s="9">
         <v>1000</v>
       </c>
-      <c r="J249" s="7" t="s">
-        <v>203</v>
-      </c>
-      <c r="K249" s="8"/>
+      <c r="J249" s="7" t="str">
+        <f t="shared" si="1"/>
+        <v>Open Order</v>
+      </c>
+      <c r="K249" s="8" t="s">
+        <v>204</v>
+      </c>
     </row>
     <row r="250" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A250" s="4" t="s">
@@ -5804,10 +5828,13 @@
       <c r="I250" s="10">
         <v>1000</v>
       </c>
-      <c r="J250" s="7" t="s">
-        <v>203</v>
-      </c>
-      <c r="K250" s="8"/>
+      <c r="J250" s="7" t="str">
+        <f t="shared" si="1"/>
+        <v>Open Order</v>
+      </c>
+      <c r="K250" s="8" t="s">
+        <v>204</v>
+      </c>
     </row>
     <row r="251" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A251" s="4" t="s">
@@ -5822,10 +5849,13 @@
       <c r="I251" s="10">
         <v>1000</v>
       </c>
-      <c r="J251" s="7" t="s">
-        <v>203</v>
-      </c>
-      <c r="K251" s="8"/>
+      <c r="J251" s="7" t="str">
+        <f t="shared" si="1"/>
+        <v>Open Order</v>
+      </c>
+      <c r="K251" s="8" t="s">
+        <v>204</v>
+      </c>
     </row>
     <row r="252" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A252" s="4" t="s">
@@ -5840,10 +5870,13 @@
       <c r="I252" s="9">
         <v>1000</v>
       </c>
-      <c r="J252" s="7" t="s">
-        <v>203</v>
-      </c>
-      <c r="K252" s="8"/>
+      <c r="J252" s="7" t="str">
+        <f t="shared" si="1"/>
+        <v>Open Order</v>
+      </c>
+      <c r="K252" s="8" t="s">
+        <v>204</v>
+      </c>
     </row>
     <row r="253" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A253" s="4" t="s">
@@ -5858,10 +5891,13 @@
       <c r="I253" s="9">
         <v>1050</v>
       </c>
-      <c r="J253" s="7" t="s">
-        <v>203</v>
-      </c>
-      <c r="K253" s="8"/>
+      <c r="J253" s="7" t="str">
+        <f t="shared" si="1"/>
+        <v>Open Order</v>
+      </c>
+      <c r="K253" s="8" t="s">
+        <v>204</v>
+      </c>
     </row>
     <row r="254" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A254" s="4" t="s">
@@ -5876,10 +5912,13 @@
       <c r="I254" s="10">
         <v>1002</v>
       </c>
-      <c r="J254" s="7" t="s">
-        <v>203</v>
-      </c>
-      <c r="K254" s="8"/>
+      <c r="J254" s="7" t="str">
+        <f t="shared" si="1"/>
+        <v>Open Order</v>
+      </c>
+      <c r="K254" s="8" t="s">
+        <v>204</v>
+      </c>
     </row>
     <row r="255" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A255" s="4" t="s">
@@ -5894,52 +5933,55 @@
       <c r="I255" s="9">
         <v>2000</v>
       </c>
-      <c r="J255" s="7" t="s">
-        <v>203</v>
-      </c>
-      <c r="K255" s="8"/>
+      <c r="J255" s="7" t="str">
+        <f t="shared" si="1"/>
+        <v>Open Order</v>
+      </c>
+      <c r="K255" s="8" t="s">
+        <v>204</v>
+      </c>
     </row>
   </sheetData>
   <autoFilter ref="A1:L255" xr:uid="{76CBFB1B-DC23-4380-8138-4D6BFF18CBC5}"/>
   <phoneticPr fontId="3" type="noConversion"/>
+  <conditionalFormatting sqref="A2:A109">
+    <cfRule type="duplicateValues" dxfId="14" priority="2233"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="A96:A98">
+    <cfRule type="duplicateValues" dxfId="13" priority="2230"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="A110">
+    <cfRule type="duplicateValues" dxfId="12" priority="2224"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="A205:A238">
+    <cfRule type="duplicateValues" dxfId="11" priority="2223"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="A205:A240">
+    <cfRule type="duplicateValues" dxfId="10" priority="2221"/>
+  </conditionalFormatting>
   <conditionalFormatting sqref="A241">
-    <cfRule type="duplicateValues" dxfId="14" priority="6"/>
+    <cfRule type="duplicateValues" dxfId="9" priority="6"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="A242:A245">
+    <cfRule type="duplicateValues" dxfId="8" priority="2199"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="A247:A255">
+    <cfRule type="duplicateValues" dxfId="7" priority="2198"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="A1:B1">
-    <cfRule type="duplicateValues" dxfId="13" priority="1919"/>
+    <cfRule type="duplicateValues" dxfId="6" priority="1919"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="D1:H1">
-    <cfRule type="duplicateValues" dxfId="12" priority="2130"/>
-    <cfRule type="duplicateValues" dxfId="11" priority="2131" stopIfTrue="1"/>
+    <cfRule type="duplicateValues" dxfId="5" priority="2130"/>
+    <cfRule type="duplicateValues" dxfId="4" priority="2131" stopIfTrue="1"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="I1">
-    <cfRule type="duplicateValues" dxfId="10" priority="1917"/>
-    <cfRule type="duplicateValues" dxfId="9" priority="1918" stopIfTrue="1"/>
+    <cfRule type="duplicateValues" dxfId="3" priority="1917"/>
+    <cfRule type="duplicateValues" dxfId="2" priority="1918" stopIfTrue="1"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="J1:L1">
-    <cfRule type="duplicateValues" dxfId="8" priority="1915"/>
-    <cfRule type="duplicateValues" dxfId="7" priority="1916" stopIfTrue="1"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="A247:A255">
-    <cfRule type="duplicateValues" dxfId="6" priority="2198"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="A242:A245">
-    <cfRule type="duplicateValues" dxfId="5" priority="2199"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="A205:A240">
-    <cfRule type="duplicateValues" dxfId="4" priority="2221"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="A205:A238">
-    <cfRule type="duplicateValues" dxfId="3" priority="2223"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="A110">
-    <cfRule type="duplicateValues" dxfId="2" priority="2224"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="A96:A98">
-    <cfRule type="duplicateValues" dxfId="1" priority="2230"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="A2:A109">
-    <cfRule type="duplicateValues" dxfId="0" priority="2233"/>
+    <cfRule type="duplicateValues" dxfId="1" priority="1915"/>
+    <cfRule type="duplicateValues" dxfId="0" priority="1916" stopIfTrue="1"/>
   </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
